--- a/data/trans_orig/P39C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P39C-Provincia-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2016</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2016 (tasa de respuesta: 97,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33905</t>
+          <t>32645</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>13074</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32951</t>
+          <t>31727</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29460</t>
+          <t>28956</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57964</t>
+          <t>57079</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>33744</t>
+          <t>32852</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60149</t>
+          <t>58227</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39680</t>
+          <t>39183</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64906</t>
+          <t>64015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79034</t>
+          <t>80057</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115230</t>
+          <t>115920</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39930</t>
+          <t>40166</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>66671</t>
+          <t>65883</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41836</t>
+          <t>42228</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67706</t>
+          <t>68696</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>89700</t>
+          <t>88890</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>126051</t>
+          <t>127285</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27736</t>
+          <t>28231</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51195</t>
+          <t>51777</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27683</t>
+          <t>28160</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50128</t>
+          <t>51164</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>61101</t>
+          <t>60201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94773</t>
+          <t>93107</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33377</t>
+          <t>34670</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58710</t>
+          <t>58815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40422</t>
+          <t>40660</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65447</t>
+          <t>65494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80244</t>
+          <t>80892</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115311</t>
+          <t>115516</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29613</t>
+          <t>30542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>53131</t>
+          <t>54588</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>22168</t>
+          <t>23667</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45476</t>
+          <t>45823</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56589</t>
+          <t>58569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>90255</t>
+          <t>91957</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,1%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140066</t>
+          <t>140797</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180111</t>
+          <t>180400</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>146433</t>
+          <t>145855</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>187864</t>
+          <t>187032</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>297659</t>
+          <t>298894</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>359057</t>
+          <t>355362</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>114873</t>
+          <t>115820</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>155539</t>
+          <t>153036</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36,56%</t>
+          <t>35,97%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>143759</t>
+          <t>144574</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>187538</t>
+          <t>187245</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>270253</t>
+          <t>273151</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>329866</t>
+          <t>332903</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27162</t>
+          <t>27894</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52119</t>
+          <t>51575</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39901</t>
+          <t>40013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68986</t>
+          <t>69704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75385</t>
+          <t>74351</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>111845</t>
+          <t>112964</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,4%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37008</t>
+          <t>38029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63683</t>
+          <t>64117</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52582</t>
+          <t>51580</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>85487</t>
+          <t>84024</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>98474</t>
+          <t>95982</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139931</t>
+          <t>139310</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27776</t>
+          <t>27832</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48958</t>
+          <t>49203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>19243</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>40275</t>
+          <t>39965</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49799</t>
+          <t>52575</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>81041</t>
+          <t>83099</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78916</t>
+          <t>78079</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>107605</t>
+          <t>110215</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69996</t>
+          <t>67119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100029</t>
+          <t>100253</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153767</t>
+          <t>153357</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>198180</t>
+          <t>197177</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,62%</t>
+          <t>34,45%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77096</t>
+          <t>76382</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107739</t>
+          <t>107208</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>102527</t>
+          <t>101098</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>136778</t>
+          <t>135162</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>186539</t>
+          <t>186292</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>230596</t>
+          <t>233466</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,79%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17695</t>
+          <t>18214</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>37647</t>
+          <t>36506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15296</t>
+          <t>15640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34254</t>
+          <t>35344</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38565</t>
+          <t>37977</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64963</t>
+          <t>65964</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17509</t>
+          <t>18277</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35771</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33881</t>
+          <t>33303</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57264</t>
+          <t>58202</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>57390</t>
+          <t>55822</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>85734</t>
+          <t>88106</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,12 +2632,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31245</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56948</t>
+          <t>57742</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25092</t>
+          <t>24975</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48274</t>
+          <t>48316</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62050</t>
+          <t>61742</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95682</t>
+          <t>95332</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53315</t>
+          <t>53513</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>83991</t>
+          <t>83400</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>56314</t>
+          <t>55596</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>88586</t>
+          <t>88283</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>117253</t>
+          <t>117698</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>162506</t>
+          <t>161462</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>75590</t>
+          <t>76063</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>109584</t>
+          <t>109609</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,3%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>64325</t>
+          <t>63883</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>96961</t>
+          <t>95823</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>148209</t>
+          <t>146027</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>196951</t>
+          <t>195040</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31578</t>
+          <t>31189</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57604</t>
+          <t>57832</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38953</t>
+          <t>38263</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>67521</t>
+          <t>66327</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77120</t>
+          <t>77176</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>114665</t>
+          <t>115568</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78523</t>
+          <t>78337</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110583</t>
+          <t>110807</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>101227</t>
+          <t>100470</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>137311</t>
+          <t>139068</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>189990</t>
+          <t>188479</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>239222</t>
+          <t>237524</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,26%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21768</t>
+          <t>21894</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42050</t>
+          <t>42178</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15242</t>
+          <t>15364</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32949</t>
+          <t>33761</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>40621</t>
+          <t>41452</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>67811</t>
+          <t>68340</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>27329</t>
+          <t>25058</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>48727</t>
+          <t>46660</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>38950</t>
+          <t>39670</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>62607</t>
+          <t>64586</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>72908</t>
+          <t>73905</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>103974</t>
+          <t>104407</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>21511</t>
+          <t>20797</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40699</t>
+          <t>40922</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32111</t>
+          <t>32543</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53627</t>
+          <t>54786</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>60108</t>
+          <t>58733</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>89298</t>
+          <t>88342</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,15%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22052</t>
+          <t>21498</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41608</t>
+          <t>41303</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>27307</t>
+          <t>27464</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48062</t>
+          <t>48665</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>54475</t>
+          <t>53938</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>83907</t>
+          <t>84618</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,09%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>21736</t>
+          <t>22279</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41582</t>
+          <t>41663</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28197</t>
+          <t>27259</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>50206</t>
+          <t>51346</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55213</t>
+          <t>55970</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>85187</t>
+          <t>85090</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>24111</t>
+          <t>23857</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>47533</t>
+          <t>46331</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>11706</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30833</t>
+          <t>30002</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>40622</t>
+          <t>40010</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>68746</t>
+          <t>66895</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>32156</t>
+          <t>33312</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>55693</t>
+          <t>55373</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>45145</t>
+          <t>45293</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>72431</t>
+          <t>72320</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,12%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>84607</t>
+          <t>84526</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>119387</t>
+          <t>119956</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,87%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>42627</t>
+          <t>42764</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>68540</t>
+          <t>67420</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>36407</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>60210</t>
+          <t>60705</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>86042</t>
+          <t>86228</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>120998</t>
+          <t>124108</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>25461</t>
+          <t>23874</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>47085</t>
+          <t>46961</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>37462</t>
+          <t>36509</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>61670</t>
+          <t>62785</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>67292</t>
+          <t>67770</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>100481</t>
+          <t>100886</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>31470</t>
+          <t>31909</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>55050</t>
+          <t>56447</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>50409</t>
+          <t>51099</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>77692</t>
+          <t>78800</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>89586</t>
+          <t>88935</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>125061</t>
+          <t>125639</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,14%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>27678</t>
+          <t>27199</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>52271</t>
+          <t>51772</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>28293</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>54106</t>
+          <t>54694</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>62842</t>
+          <t>61359</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>97306</t>
+          <t>96814</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>88732</t>
+          <t>86582</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>125621</t>
+          <t>124026</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>87750</t>
+          <t>86046</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>122154</t>
+          <t>121799</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>182412</t>
+          <t>183484</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>236732</t>
+          <t>233276</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>87223</t>
+          <t>87902</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>127082</t>
+          <t>124691</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>131756</t>
+          <t>131449</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>173929</t>
+          <t>174849</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>229609</t>
+          <t>230446</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>290359</t>
+          <t>289860</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,31%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>39783</t>
+          <t>39537</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>67456</t>
+          <t>67115</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>46218</t>
+          <t>48672</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>76541</t>
+          <t>76913</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>93147</t>
+          <t>93365</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>135562</t>
+          <t>133765</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>70380</t>
+          <t>71545</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>105620</t>
+          <t>103879</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>105295</t>
+          <t>107128</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>144942</t>
+          <t>148496</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>187568</t>
+          <t>185518</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>242116</t>
+          <t>239455</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>52722</t>
+          <t>53115</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>85861</t>
+          <t>84732</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>38097</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>64748</t>
+          <t>65219</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>98122</t>
+          <t>98359</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>141803</t>
+          <t>140655</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>149751</t>
+          <t>154033</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>197394</t>
+          <t>199060</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>173169</t>
+          <t>172312</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>220577</t>
+          <t>219890</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,12 +5668,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>336761</t>
+          <t>339194</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>402861</t>
+          <t>404104</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>180721</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>232300</t>
+          <t>228577</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>228673</t>
+          <t>230794</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>281631</t>
+          <t>282523</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>428287</t>
+          <t>428563</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>499823</t>
+          <t>500872</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,23%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>80707</t>
+          <t>80980</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>118775</t>
+          <t>118916</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>97693</t>
+          <t>95810</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>139581</t>
+          <t>137759</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>188587</t>
+          <t>193218</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>243275</t>
+          <t>245261</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>76852</t>
+          <t>78813</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>112875</t>
+          <t>113805</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>98129</t>
+          <t>100082</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>141702</t>
+          <t>141531</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>189095</t>
+          <t>187414</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>242824</t>
+          <t>241518</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,47%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>281520</t>
+          <t>279654</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>350513</t>
+          <t>348754</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>221858</t>
+          <t>221359</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>284715</t>
+          <t>283908</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>516579</t>
+          <t>521810</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>611179</t>
+          <t>612555</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>680673</t>
+          <t>680428</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>773417</t>
+          <t>773753</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6315,12 +6315,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>733677</t>
+          <t>732802</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>833040</t>
+          <t>830799</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1435423</t>
+          <t>1438837</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1571228</t>
+          <t>1572458</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,85%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>721375</t>
+          <t>720362</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>816625</t>
+          <t>815338</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>27,34%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>865630</t>
+          <t>865861</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>967719</t>
+          <t>964915</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6468,7 +6468,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1618075</t>
+          <t>1613853</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1758349</t>
+          <t>1752680</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>326974</t>
+          <t>330688</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>405139</t>
+          <t>404019</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>384799</t>
+          <t>389115</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>469729</t>
+          <t>470399</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>742969</t>
+          <t>740085</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>849474</t>
+          <t>846161</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>432525</t>
+          <t>432030</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>508543</t>
+          <t>510298</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>586564</t>
+          <t>585361</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>678512</t>
+          <t>677930</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1039868</t>
+          <t>1040577</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1163914</t>
+          <t>1165572</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6910,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2023</t>
+          <t>Población según el tiempo transcurrido desde la última vez que le midieron la glucosa en 2023 (tasa de respuesta: 99,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7105,12 +7105,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9327</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32827</t>
+          <t>33742</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2270</t>
+          <t>2554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>9077</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7155,12 +7155,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13214</t>
+          <t>13320</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>37559</t>
+          <t>40824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7190,12 +7190,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,96%</t>
         </is>
       </c>
     </row>
@@ -7218,12 +7218,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>65944</t>
+          <t>64402</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106389</t>
+          <t>102434</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7233,12 +7233,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>58333</t>
+          <t>56919</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84543</t>
+          <t>84419</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7268,12 +7268,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>128278</t>
+          <t>129228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>176206</t>
+          <t>179780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7303,12 +7303,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,63%</t>
         </is>
       </c>
     </row>
@@ -7331,12 +7331,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>55193</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>94305</t>
+          <t>93609</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7346,12 +7346,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65901</t>
+          <t>66314</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90872</t>
+          <t>91096</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7381,12 +7381,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>128732</t>
+          <t>128215</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>176201</t>
+          <t>175114</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>29,83%</t>
         </is>
       </c>
     </row>
@@ -7444,12 +7444,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37430</t>
+          <t>36892</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>68946</t>
+          <t>67907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33528</t>
+          <t>33322</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52637</t>
+          <t>51816</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7494,12 +7494,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75686</t>
+          <t>76006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>112482</t>
+          <t>110234</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7529,12 +7529,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>67479</t>
+          <t>66579</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>99312</t>
+          <t>100624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7592,12 +7592,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>77924</t>
+          <t>78810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104262</t>
+          <t>103832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7607,12 +7607,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7627,12 +7627,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>151708</t>
+          <t>150709</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>194157</t>
+          <t>193597</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7642,12 +7642,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -7787,12 +7787,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46903</t>
+          <t>47408</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81879</t>
+          <t>85233</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56525</t>
+          <t>56868</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82365</t>
+          <t>82014</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7837,12 +7837,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110815</t>
+          <t>111400</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155998</t>
+          <t>158211</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,42%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>138076</t>
+          <t>136819</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183576</t>
+          <t>185232</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>163237</t>
+          <t>162655</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>197953</t>
+          <t>196458</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309263</t>
+          <t>311481</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>366606</t>
+          <t>369386</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>45,35%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>65658</t>
+          <t>66062</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>104386</t>
+          <t>105183</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75426</t>
+          <t>75717</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>103977</t>
+          <t>103919</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>150507</t>
+          <t>146281</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>197529</t>
+          <t>194075</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>23,83%</t>
         </is>
       </c>
     </row>
@@ -8126,12 +8126,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>20281</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46312</t>
+          <t>49950</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8141,12 +8141,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8161,12 +8161,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>19777</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35175</t>
+          <t>36003</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8176,12 +8176,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8196,12 +8196,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43536</t>
+          <t>43110</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74652</t>
+          <t>75207</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -8239,12 +8239,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35126</t>
+          <t>34192</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>63424</t>
+          <t>61395</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8274,12 +8274,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>56757</t>
+          <t>57140</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>81521</t>
+          <t>84515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8309,12 +8309,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>97571</t>
+          <t>95775</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>136449</t>
+          <t>135157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,59%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21375</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>47195</t>
+          <t>45735</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19128</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37405</t>
+          <t>37230</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45231</t>
+          <t>45013</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74723</t>
+          <t>78005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41285</t>
+          <t>41497</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70769</t>
+          <t>69041</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50763</t>
+          <t>50240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74413</t>
+          <t>75704</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>99502</t>
+          <t>97233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>134928</t>
+          <t>133249</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>20,99%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76540</t>
+          <t>76272</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107516</t>
+          <t>108832</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>91674</t>
+          <t>91441</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>119290</t>
+          <t>120849</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>177109</t>
+          <t>176529</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>221280</t>
+          <t>217938</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8780,12 +8780,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -8808,12 +8808,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30033</t>
+          <t>30254</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50467</t>
+          <t>50255</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8823,12 +8823,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8843,12 +8843,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54619</t>
+          <t>53891</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78573</t>
+          <t>79186</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90383</t>
+          <t>90603</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>123231</t>
+          <t>121276</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -8921,12 +8921,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63013</t>
+          <t>63752</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91358</t>
+          <t>90877</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8956,12 +8956,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67481</t>
+          <t>67781</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>93557</t>
+          <t>94155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8991,12 +8991,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>139819</t>
+          <t>140175</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>176238</t>
+          <t>176488</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,8%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13860</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35751</t>
+          <t>34723</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20435</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42475</t>
+          <t>43251</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39629</t>
+          <t>39041</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71242</t>
+          <t>70625</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44513</t>
+          <t>44034</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>76160</t>
+          <t>77603</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49587</t>
+          <t>49863</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>84958</t>
+          <t>83988</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>100284</t>
+          <t>102035</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>148540</t>
+          <t>148804</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43766</t>
+          <t>43951</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>76844</t>
+          <t>75856</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77870</t>
+          <t>79278</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>185293</t>
+          <t>174562</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>48,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>133281</t>
+          <t>136232</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>236783</t>
+          <t>242272</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -9490,12 +9490,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>36887</t>
+          <t>37262</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69826</t>
+          <t>68977</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9505,12 +9505,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30217</t>
+          <t>32345</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54900</t>
+          <t>57437</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9560,12 +9560,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76720</t>
+          <t>76611</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>120165</t>
+          <t>116715</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,78%</t>
         </is>
       </c>
     </row>
@@ -9603,12 +9603,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53291</t>
+          <t>53183</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82908</t>
+          <t>83680</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9618,12 +9618,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9638,12 +9638,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>74958</t>
+          <t>80265</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>128981</t>
+          <t>129170</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>145932</t>
+          <t>145462</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>201913</t>
+          <t>202256</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,54%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3793</t>
+          <t>3751</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12688</t>
+          <t>12896</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>4689</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>13087</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10180</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22224</t>
+          <t>22427</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -9946,12 +9946,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20160</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35636</t>
+          <t>35973</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -9961,12 +9961,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9981,12 +9981,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>24711</t>
+          <t>25115</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39243</t>
+          <t>39069</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10016,12 +10016,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>48908</t>
+          <t>49057</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>70268</t>
+          <t>70059</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>
@@ -10059,12 +10059,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>62640</t>
+          <t>61879</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>82199</t>
+          <t>81872</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10074,12 +10074,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>65956</t>
+          <t>66636</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>84241</t>
+          <t>84371</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>35,99%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>134941</t>
+          <t>133899</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>160118</t>
+          <t>160294</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,82%</t>
         </is>
       </c>
     </row>
@@ -10172,12 +10172,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18031</t>
+          <t>18084</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>33205</t>
+          <t>33141</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -10187,12 +10187,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33054</t>
+          <t>33296</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>47432</t>
+          <t>48213</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10242,12 +10242,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>55673</t>
+          <t>54642</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>75851</t>
+          <t>75315</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,94%</t>
         </is>
       </c>
     </row>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>8921</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>19759</t>
+          <t>20296</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22554</t>
+          <t>23360</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>35439</t>
+          <t>35337</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10355,12 +10355,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>35299</t>
+          <t>34809</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>51258</t>
+          <t>51263</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -10370,7 +10370,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>46819</t>
+          <t>48111</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15409</t>
+          <t>15715</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>32247</t>
+          <t>31853</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>45200</t>
+          <t>44715</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>72889</t>
+          <t>73446</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -10628,12 +10628,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>49236</t>
+          <t>49921</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>76689</t>
+          <t>75288</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -10643,12 +10643,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>38905</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>59654</t>
+          <t>59362</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10698,12 +10698,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>95210</t>
+          <t>93989</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>127734</t>
+          <t>128686</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,48%</t>
         </is>
       </c>
     </row>
@@ -10741,12 +10741,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>54299</t>
+          <t>54871</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>78577</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10776,12 +10776,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>58929</t>
+          <t>58254</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>80164</t>
+          <t>80198</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -10791,12 +10791,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>119166</t>
+          <t>119071</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>152518</t>
+          <t>153650</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -10826,12 +10826,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,42%</t>
         </is>
       </c>
     </row>
@@ -10854,12 +10854,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>31275</t>
+          <t>30630</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>50154</t>
+          <t>50702</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -10869,12 +10869,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10889,12 +10889,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>35431</t>
+          <t>35411</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>55609</t>
+          <t>52726</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -10904,12 +10904,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10924,12 +10924,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>70812</t>
+          <t>70806</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>96421</t>
+          <t>96730</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -10944,7 +10944,7 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -10967,12 +10967,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>44749</t>
+          <t>43652</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>67228</t>
+          <t>65610</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -10982,12 +10982,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -11002,12 +11002,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>53562</t>
+          <t>54222</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>74490</t>
+          <t>74265</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -11017,12 +11017,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11037,12 +11037,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>103164</t>
+          <t>104581</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>134381</t>
+          <t>134701</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -11052,12 +11052,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19160</t>
+          <t>19139</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>39327</t>
+          <t>39580</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -11217,7 +11217,7 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>12861</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>46889</t>
+          <t>47023</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>34950</t>
+          <t>33237</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>78599</t>
+          <t>78878</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -11310,12 +11310,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>73331</t>
+          <t>73783</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>114931</t>
+          <t>115052</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -11325,12 +11325,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11345,12 +11345,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>47459</t>
+          <t>52461</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>153443</t>
+          <t>155135</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -11360,12 +11360,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>116623</t>
+          <t>118963</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>248937</t>
+          <t>248470</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -11395,12 +11395,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -11423,12 +11423,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>147382</t>
+          <t>145491</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>194083</t>
+          <t>194485</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>233864</t>
+          <t>232617</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>600974</t>
+          <t>594457</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>404742</t>
+          <t>403161</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>853553</t>
+          <t>817276</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -11508,12 +11508,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>64,03%</t>
         </is>
       </c>
     </row>
@@ -11536,12 +11536,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>73654</t>
+          <t>72605</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>107329</t>
+          <t>107535</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>43338</t>
+          <t>42355</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>137396</t>
+          <t>138153</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>113439</t>
+          <t>114862</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>231499</t>
+          <t>228899</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -11621,12 +11621,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,93%</t>
         </is>
       </c>
     </row>
@@ -11649,12 +11649,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>99151</t>
+          <t>97427</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>136241</t>
+          <t>134670</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11684,12 +11684,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>72216</t>
+          <t>72254</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>227196</t>
+          <t>229064</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -11699,12 +11699,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11719,12 +11719,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>165831</t>
+          <t>179320</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>346134</t>
+          <t>345095</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -11734,12 +11734,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,03%</t>
         </is>
       </c>
     </row>
@@ -11879,12 +11879,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>9285</t>
+          <t>8915</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>23372</t>
+          <t>24297</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>13753</t>
+          <t>14727</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>29106</t>
+          <t>29389</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>26389</t>
+          <t>27007</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>47949</t>
+          <t>48109</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -11964,12 +11964,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>117098</t>
+          <t>117937</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>153966</t>
+          <t>153938</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -12027,12 +12027,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>115972</t>
+          <t>115857</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>148461</t>
+          <t>149533</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -12042,12 +12042,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12062,12 +12062,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>243315</t>
+          <t>242973</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>292081</t>
+          <t>290512</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,67%</t>
         </is>
       </c>
     </row>
@@ -12105,12 +12105,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>123967</t>
+          <t>125619</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>159100</t>
+          <t>158721</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -12120,12 +12120,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12140,12 +12140,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>157870</t>
+          <t>158845</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>190901</t>
+          <t>192553</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -12155,12 +12155,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>292678</t>
+          <t>292412</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>342003</t>
+          <t>341824</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,26%</t>
         </is>
       </c>
     </row>
@@ -12218,12 +12218,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>86075</t>
+          <t>86334</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>116423</t>
+          <t>117939</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -12233,12 +12233,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>99124</t>
+          <t>100473</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>128331</t>
+          <t>129333</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12288,12 +12288,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>195505</t>
+          <t>193349</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>236238</t>
+          <t>236355</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -12303,12 +12303,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -12331,12 +12331,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>16712</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>34146</t>
+          <t>34658</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12366,12 +12366,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>47690</t>
+          <t>48107</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>69721</t>
+          <t>70168</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>70869</t>
+          <t>69207</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>99653</t>
+          <t>98558</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -12416,12 +12416,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,74%</t>
         </is>
       </c>
     </row>
@@ -12561,12 +12561,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>188895</t>
+          <t>189985</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>252832</t>
+          <t>253249</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -12576,12 +12576,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12596,12 +12596,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>170455</t>
+          <t>169140</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>243935</t>
+          <t>245341</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -12611,12 +12611,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12631,12 +12631,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>370556</t>
+          <t>376305</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>476555</t>
+          <t>477555</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -12646,12 +12646,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -12674,12 +12674,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>619599</t>
+          <t>624114</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>716986</t>
+          <t>719194</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -12689,12 +12689,12 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>539355</t>
+          <t>514877</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>763920</t>
+          <t>764924</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -12724,12 +12724,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12744,12 +12744,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1198886</t>
+          <t>1198206</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1452057</t>
+          <t>1452035</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -12787,12 +12787,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>708105</t>
+          <t>709204</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>805649</t>
+          <t>807642</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -12802,12 +12802,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12822,12 +12822,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>923479</t>
+          <t>917760</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1571757</t>
+          <t>1561249</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -12837,12 +12837,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>49,83%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12857,12 +12857,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1669950</t>
+          <t>1666576</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2346436</t>
+          <t>2360790</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -12872,12 +12872,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>41,53%</t>
         </is>
       </c>
     </row>
@@ -12900,12 +12900,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>386905</t>
+          <t>388860</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>466108</t>
+          <t>465000</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -12915,12 +12915,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12935,12 +12935,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>360904</t>
+          <t>371900</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>519477</t>
+          <t>521615</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -12950,12 +12950,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12970,12 +12970,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>784907</t>
+          <t>794632</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>954601</t>
+          <t>966083</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -12985,12 +12985,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -13013,12 +13013,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>446863</t>
+          <t>443283</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>527397</t>
+          <t>522492</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -13028,12 +13028,12 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>499434</t>
+          <t>527623</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>724281</t>
+          <t>726740</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -13063,12 +13063,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1021834</t>
+          <t>1002787</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1220016</t>
+          <t>1217733</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -13098,12 +13098,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P39C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P39C-Provincia-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12963</t>
+          <t>12439</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32645</t>
+          <t>31281</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13074</t>
+          <t>14157</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31727</t>
+          <t>32553</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28956</t>
+          <t>30740</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57079</t>
+          <t>57396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>32852</t>
+          <t>33802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58227</t>
+          <t>57842</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>39183</t>
+          <t>39254</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64015</t>
+          <t>63663</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>80057</t>
+          <t>79341</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115920</t>
+          <t>115146</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40166</t>
+          <t>41119</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65883</t>
+          <t>67244</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42228</t>
+          <t>41842</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68696</t>
+          <t>67586</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>88890</t>
+          <t>88866</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>127285</t>
+          <t>125085</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28231</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51777</t>
+          <t>50709</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28160</t>
+          <t>27263</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51164</t>
+          <t>50129</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60201</t>
+          <t>61335</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93107</t>
+          <t>93365</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>33217</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58815</t>
+          <t>57561</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1198,12 +1198,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>40660</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>65494</t>
+          <t>65157</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1253,12 +1253,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>80892</t>
+          <t>80206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115516</t>
+          <t>116917</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,9%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30542</t>
+          <t>30163</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54588</t>
+          <t>54377</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23667</t>
+          <t>22094</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>45674</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58569</t>
+          <t>59700</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>91957</t>
+          <t>92739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>140797</t>
+          <t>141221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>180400</t>
+          <t>180228</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>145855</t>
+          <t>146242</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>187032</t>
+          <t>186320</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>298894</t>
+          <t>297773</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>355362</t>
+          <t>357044</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,2%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>115820</t>
+          <t>115309</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>153036</t>
+          <t>157185</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>144574</t>
+          <t>145431</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>187245</t>
+          <t>188890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>273151</t>
+          <t>270774</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>332903</t>
+          <t>328821</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,11%</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27894</t>
+          <t>28391</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51575</t>
+          <t>52495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1767,12 +1767,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40013</t>
+          <t>40121</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>69704</t>
+          <t>68612</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1802,12 +1802,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1822,12 +1822,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>74351</t>
+          <t>72965</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112964</t>
+          <t>109903</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -1865,12 +1865,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38029</t>
+          <t>37261</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>64117</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1880,12 +1880,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1900,12 +1900,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51580</t>
+          <t>53935</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84024</t>
+          <t>84965</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1915,12 +1915,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1935,12 +1935,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95982</t>
+          <t>97939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>139310</t>
+          <t>139932</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1950,12 +1950,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27832</t>
+          <t>27225</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49203</t>
+          <t>48684</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>18834</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39965</t>
+          <t>39019</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52575</t>
+          <t>52201</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83099</t>
+          <t>83714</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78079</t>
+          <t>77794</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110215</t>
+          <t>106094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67119</t>
+          <t>69464</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100253</t>
+          <t>99020</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153357</t>
+          <t>154506</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>197177</t>
+          <t>196654</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,36%</t>
         </is>
       </c>
     </row>
@@ -2321,12 +2321,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76382</t>
+          <t>77426</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>107208</t>
+          <t>107602</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2336,12 +2336,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>39,25%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>101098</t>
+          <t>103518</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>135162</t>
+          <t>136654</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>45,17%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2391,12 +2391,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>186292</t>
+          <t>189057</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>233466</t>
+          <t>234581</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,98%</t>
         </is>
       </c>
     </row>
@@ -2434,12 +2434,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>18214</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36506</t>
+          <t>36951</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15640</t>
+          <t>15395</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35344</t>
+          <t>34413</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2504,12 +2504,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37977</t>
+          <t>37827</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>65964</t>
+          <t>64258</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,23%</t>
         </is>
       </c>
     </row>
@@ -2547,12 +2547,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18277</t>
+          <t>17137</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36624</t>
+          <t>36237</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2562,12 +2562,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2582,12 +2582,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33303</t>
+          <t>34215</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58202</t>
+          <t>58453</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2597,12 +2597,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2617,12 +2617,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>55822</t>
+          <t>55539</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>88106</t>
+          <t>88085</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31796</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57742</t>
+          <t>58891</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>24975</t>
+          <t>24809</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>48316</t>
+          <t>47218</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61742</t>
+          <t>62715</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95332</t>
+          <t>96990</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -2890,12 +2890,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>53513</t>
+          <t>53711</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>83400</t>
+          <t>83848</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,12 +2905,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2925,12 +2925,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>55596</t>
+          <t>54292</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>88283</t>
+          <t>85601</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2940,12 +2940,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2960,12 +2960,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>117698</t>
+          <t>119046</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>161462</t>
+          <t>161689</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2975,12 +2975,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,32%</t>
         </is>
       </c>
     </row>
@@ -3003,12 +3003,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>76063</t>
+          <t>76445</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>109609</t>
+          <t>108189</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3018,12 +3018,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>63883</t>
+          <t>62967</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>95823</t>
+          <t>94592</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3053,12 +3053,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>146027</t>
+          <t>146913</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>195040</t>
+          <t>193671</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>27,93%</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3116,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31189</t>
+          <t>32169</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57832</t>
+          <t>58434</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3131,12 +3131,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>39531</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66327</t>
+          <t>67359</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77176</t>
+          <t>77391</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>115568</t>
+          <t>114526</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3229,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>78337</t>
+          <t>76650</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>110807</t>
+          <t>110467</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3244,12 +3244,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3264,12 +3264,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>100470</t>
+          <t>100394</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>139068</t>
+          <t>137264</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3299,12 +3299,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>188479</t>
+          <t>188022</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>237524</t>
+          <t>239058</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21894</t>
+          <t>21013</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>42178</t>
+          <t>41457</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3474,12 +3474,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15364</t>
+          <t>15066</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>33761</t>
+          <t>34298</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>41452</t>
+          <t>41004</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>69804</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,87%</t>
         </is>
       </c>
     </row>
@@ -3572,12 +3572,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25058</t>
+          <t>26595</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>46660</t>
+          <t>46616</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3607,12 +3607,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>39670</t>
+          <t>39967</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>64586</t>
+          <t>63799</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3642,12 +3642,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>73905</t>
+          <t>72855</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>104407</t>
+          <t>103987</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>20797</t>
+          <t>21048</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40922</t>
+          <t>41873</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3720,12 +3720,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>32543</t>
+          <t>31885</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>54786</t>
+          <t>53834</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>58733</t>
+          <t>59849</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>88342</t>
+          <t>89825</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>25,57%</t>
         </is>
       </c>
     </row>
@@ -3798,12 +3798,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>21498</t>
+          <t>22317</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>41303</t>
+          <t>41507</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3813,12 +3813,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>27464</t>
+          <t>26205</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48665</t>
+          <t>49007</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>53938</t>
+          <t>53786</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>84618</t>
+          <t>83154</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -3911,12 +3911,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>22279</t>
+          <t>21160</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>41663</t>
+          <t>41772</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3946,12 +3946,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>27259</t>
+          <t>28490</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>51346</t>
+          <t>52643</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3981,12 +3981,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>55970</t>
+          <t>53579</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>85090</t>
+          <t>85037</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -4141,12 +4141,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>23857</t>
+          <t>22915</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>46331</t>
+          <t>44602</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4156,12 +4156,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4176,12 +4176,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>11706</t>
+          <t>12137</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>30002</t>
+          <t>30308</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4211,12 +4211,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>40010</t>
+          <t>39752</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>66895</t>
+          <t>68664</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>33312</t>
+          <t>33075</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>55373</t>
+          <t>56689</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>45293</t>
+          <t>44786</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>72320</t>
+          <t>74048</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4324,12 +4324,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>84526</t>
+          <t>85086</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>119956</t>
+          <t>121258</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -4367,12 +4367,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>42764</t>
+          <t>43455</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>67420</t>
+          <t>68214</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4402,12 +4402,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>35752</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>60705</t>
+          <t>59936</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4437,12 +4437,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>86228</t>
+          <t>85220</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>124108</t>
+          <t>119733</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>26,82%</t>
         </is>
       </c>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>23874</t>
+          <t>25052</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>46961</t>
+          <t>47324</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4495,12 +4495,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>36509</t>
+          <t>36323</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>62785</t>
+          <t>61865</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4530,12 +4530,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4550,12 +4550,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>67770</t>
+          <t>68056</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>100886</t>
+          <t>100111</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4565,12 +4565,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>31909</t>
+          <t>32393</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>56447</t>
+          <t>57108</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>51099</t>
+          <t>48673</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>78800</t>
+          <t>76948</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>88935</t>
+          <t>88487</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>125639</t>
+          <t>125196</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4678,12 +4678,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -4823,12 +4823,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>27199</t>
+          <t>27468</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>51772</t>
+          <t>53206</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4838,12 +4838,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>29617</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>54694</t>
+          <t>54191</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>61359</t>
+          <t>63500</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>96814</t>
+          <t>97323</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -4936,12 +4936,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>86582</t>
+          <t>85748</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>124026</t>
+          <t>123691</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4951,12 +4951,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>86046</t>
+          <t>86600</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>121799</t>
+          <t>122342</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4986,12 +4986,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>183484</t>
+          <t>182262</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>233276</t>
+          <t>234674</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,97%</t>
         </is>
       </c>
     </row>
@@ -5049,12 +5049,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>87902</t>
+          <t>88590</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>124691</t>
+          <t>126505</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5064,12 +5064,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>131449</t>
+          <t>131585</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>174849</t>
+          <t>171059</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>230446</t>
+          <t>230199</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>289860</t>
+          <t>288135</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>39537</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>67115</t>
+          <t>67575</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5177,12 +5177,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>48672</t>
+          <t>46875</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>76913</t>
+          <t>76463</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>93365</t>
+          <t>94475</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>133765</t>
+          <t>137148</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,76%</t>
         </is>
       </c>
     </row>
@@ -5275,12 +5275,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>71545</t>
+          <t>69274</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>103879</t>
+          <t>105227</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5290,12 +5290,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>107128</t>
+          <t>107954</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>148496</t>
+          <t>148408</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>185518</t>
+          <t>188111</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>239455</t>
+          <t>242490</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5360,12 +5360,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -5505,12 +5505,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>53115</t>
+          <t>53752</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>84732</t>
+          <t>83965</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>38097</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>65219</t>
+          <t>66763</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>98359</t>
+          <t>97679</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>140655</t>
+          <t>139012</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -5618,12 +5618,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>154033</t>
+          <t>151126</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>199060</t>
+          <t>197943</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5633,12 +5633,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>30,89%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5653,12 +5653,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>172312</t>
+          <t>173292</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>219890</t>
+          <t>219874</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>339194</t>
+          <t>336908</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>404104</t>
+          <t>406358</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5703,12 +5703,12 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>180721</t>
+          <t>182501</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>228577</t>
+          <t>232979</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5766,12 +5766,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>230794</t>
+          <t>229432</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>282523</t>
+          <t>284717</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5801,12 +5801,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>428563</t>
+          <t>428863</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>500872</t>
+          <t>498636</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5816,12 +5816,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>80980</t>
+          <t>81192</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>118916</t>
+          <t>118861</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5859,12 +5859,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5879,12 +5879,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>95810</t>
+          <t>98408</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>137759</t>
+          <t>139937</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5894,12 +5894,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5914,12 +5914,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>193218</t>
+          <t>189547</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>245261</t>
+          <t>245092</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5929,12 +5929,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -5957,12 +5957,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>78813</t>
+          <t>77159</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>113805</t>
+          <t>112665</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5972,12 +5972,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5992,12 +5992,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>100082</t>
+          <t>99920</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>141531</t>
+          <t>140392</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6007,12 +6007,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>187414</t>
+          <t>186904</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>241518</t>
+          <t>242705</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6042,12 +6042,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>279654</t>
+          <t>278571</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>348754</t>
+          <t>346149</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6202,12 +6202,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6222,12 +6222,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>221359</t>
+          <t>223808</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>283908</t>
+          <t>282967</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6237,12 +6237,12 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6257,12 +6257,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>521810</t>
+          <t>521245</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>612555</t>
+          <t>610434</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -6300,12 +6300,12 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>680428</t>
+          <t>680430</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>773753</t>
+          <t>772857</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6335,12 +6335,12 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>732802</t>
+          <t>731722</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>830799</t>
+          <t>828586</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6350,12 +6350,12 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1438837</t>
+          <t>1439271</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1572458</t>
+          <t>1573771</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -6385,12 +6385,12 @@
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,87%</t>
         </is>
       </c>
     </row>
@@ -6413,12 +6413,12 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>720362</t>
+          <t>722238</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>815338</t>
+          <t>820541</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6428,12 +6428,12 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>865861</t>
+          <t>864666</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>964915</t>
+          <t>961592</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6463,12 +6463,12 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6483,12 +6483,12 @@
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1613853</t>
+          <t>1615897</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>1752680</t>
+          <t>1762044</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -6498,12 +6498,12 @@
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -6526,12 +6526,12 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>330688</t>
+          <t>328465</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>404019</t>
+          <t>399353</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -6561,12 +6561,12 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>389115</t>
+          <t>393375</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>470399</t>
+          <t>470133</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6576,12 +6576,12 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6596,12 +6596,12 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>740085</t>
+          <t>744716</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>846161</t>
+          <t>851703</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -6611,12 +6611,12 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -6639,12 +6639,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>432030</t>
+          <t>427808</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>510298</t>
+          <t>510365</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -6674,12 +6674,12 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>585361</t>
+          <t>585189</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>677930</t>
+          <t>673185</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
@@ -6689,12 +6689,12 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6709,12 +6709,12 @@
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1040577</t>
+          <t>1038781</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1165572</t>
+          <t>1163154</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -7100,32 +7100,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>18308</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9110</t>
+          <t>10501</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33742</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7135,32 +7135,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>9197</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7170,32 +7170,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21632</t>
+          <t>23435</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>15162</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40824</t>
+          <t>34555</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -7213,32 +7213,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>81478</t>
+          <t>93133</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>64402</t>
+          <t>77180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>102434</t>
+          <t>112326</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>36,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7248,32 +7248,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>69511</t>
+          <t>78969</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>56919</t>
+          <t>66525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84419</t>
+          <t>93289</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7283,32 +7283,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>150989</t>
+          <t>172102</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>129228</t>
+          <t>151954</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>179780</t>
+          <t>194664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -7326,32 +7326,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>71373</t>
+          <t>63300</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>55193</t>
+          <t>48193</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93609</t>
+          <t>80319</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7361,32 +7361,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>78038</t>
+          <t>84961</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>66314</t>
+          <t>73721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91096</t>
+          <t>97857</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7396,32 +7396,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>149411</t>
+          <t>148260</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>128215</t>
+          <t>128410</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>175114</t>
+          <t>169353</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -7439,32 +7439,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50230</t>
+          <t>50269</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36892</t>
+          <t>38093</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67907</t>
+          <t>64654</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7474,32 +7474,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>41986</t>
+          <t>45722</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33322</t>
+          <t>36997</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51816</t>
+          <t>56379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7509,22 +7509,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>92216</t>
+          <t>95991</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>76006</t>
+          <t>80599</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110234</t>
+          <t>113383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -7534,7 +7534,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,22%</t>
         </is>
       </c>
     </row>
@@ -7552,32 +7552,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>82339</t>
+          <t>85668</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>66579</t>
+          <t>71764</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>100624</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7587,32 +7587,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>90362</t>
+          <t>96940</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>78810</t>
+          <t>83788</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>103832</t>
+          <t>110832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,44%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7622,32 +7622,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>172701</t>
+          <t>182608</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>150709</t>
+          <t>165116</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>193597</t>
+          <t>203927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,76%</t>
         </is>
       </c>
     </row>
@@ -7665,17 +7665,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>301984</t>
+          <t>310678</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>301984</t>
+          <t>310678</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>301984</t>
+          <t>310678</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7700,17 +7700,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>284964</t>
+          <t>311718</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>284964</t>
+          <t>311718</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>284964</t>
+          <t>311718</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7735,17 +7735,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>586948</t>
+          <t>622396</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>586948</t>
+          <t>622396</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>586948</t>
+          <t>622396</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7782,32 +7782,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>62845</t>
+          <t>64959</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>47408</t>
+          <t>49478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85233</t>
+          <t>85028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7817,32 +7817,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>69213</t>
+          <t>73709</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>56868</t>
+          <t>61595</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>82014</t>
+          <t>88365</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7852,32 +7852,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>132058</t>
+          <t>138668</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111400</t>
+          <t>116964</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158211</t>
+          <t>163948</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -7895,32 +7895,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>159803</t>
+          <t>166805</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136819</t>
+          <t>143717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>185232</t>
+          <t>188886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7930,32 +7930,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>179357</t>
+          <t>191964</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>162655</t>
+          <t>174118</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>196458</t>
+          <t>209154</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7965,32 +7965,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>339160</t>
+          <t>358769</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>311481</t>
+          <t>330053</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369386</t>
+          <t>390006</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -8008,32 +8008,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>82553</t>
+          <t>83321</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>66062</t>
+          <t>64086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105183</t>
+          <t>103803</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8043,32 +8043,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>88990</t>
+          <t>92519</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75717</t>
+          <t>79175</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>103919</t>
+          <t>108428</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8078,32 +8078,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>171544</t>
+          <t>175840</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>146281</t>
+          <t>154631</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>194075</t>
+          <t>200011</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,44%</t>
         </is>
       </c>
     </row>
@@ -8121,32 +8121,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>29767</t>
+          <t>30201</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20281</t>
+          <t>19801</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>49950</t>
+          <t>45204</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8156,32 +8156,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>26580</t>
+          <t>29255</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19777</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36003</t>
+          <t>39057</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8191,32 +8191,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>56347</t>
+          <t>59456</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>43110</t>
+          <t>45261</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75207</t>
+          <t>76171</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -8234,32 +8234,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>46566</t>
+          <t>50170</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34192</t>
+          <t>38054</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>61395</t>
+          <t>68449</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8269,32 +8269,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>68843</t>
+          <t>70559</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>57140</t>
+          <t>58260</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84515</t>
+          <t>85236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8304,32 +8304,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>115409</t>
+          <t>120729</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95775</t>
+          <t>101269</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>135157</t>
+          <t>141443</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -8347,17 +8347,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>381534</t>
+          <t>395456</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>381534</t>
+          <t>395456</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>381534</t>
+          <t>395456</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8382,17 +8382,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>432983</t>
+          <t>458006</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>432983</t>
+          <t>458006</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>432983</t>
+          <t>458006</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8417,17 +8417,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>814517</t>
+          <t>853462</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>814517</t>
+          <t>853462</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>814517</t>
+          <t>853462</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8464,32 +8464,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>32295</t>
+          <t>34238</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21271</t>
+          <t>22907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45735</t>
+          <t>47100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8499,32 +8499,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>26613</t>
+          <t>27758</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18486</t>
+          <t>19677</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37230</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8534,32 +8534,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>58907</t>
+          <t>61996</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45013</t>
+          <t>48379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>78005</t>
+          <t>81065</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,64%</t>
         </is>
       </c>
     </row>
@@ -8577,32 +8577,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>53996</t>
+          <t>53973</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41497</t>
+          <t>42083</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69041</t>
+          <t>69446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8612,32 +8612,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>61476</t>
+          <t>64959</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50240</t>
+          <t>53685</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75704</t>
+          <t>79593</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8647,32 +8647,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>115472</t>
+          <t>118932</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>97233</t>
+          <t>101086</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>133249</t>
+          <t>139550</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -8690,32 +8690,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>91925</t>
+          <t>92047</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>76272</t>
+          <t>75790</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>108832</t>
+          <t>107350</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8725,32 +8725,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>105700</t>
+          <t>104803</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>91441</t>
+          <t>91593</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>120849</t>
+          <t>119328</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,29%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8760,32 +8760,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>197626</t>
+          <t>196850</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>176529</t>
+          <t>176678</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>217938</t>
+          <t>217036</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>33,85%</t>
         </is>
       </c>
     </row>
@@ -8803,32 +8803,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40049</t>
+          <t>39373</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30254</t>
+          <t>30099</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50255</t>
+          <t>50125</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8838,32 +8838,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>65351</t>
+          <t>65996</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53891</t>
+          <t>55145</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79186</t>
+          <t>79188</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8873,32 +8873,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>105400</t>
+          <t>105370</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90603</t>
+          <t>90568</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121276</t>
+          <t>122162</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -8916,32 +8916,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>76938</t>
+          <t>75675</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>63752</t>
+          <t>62099</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>90877</t>
+          <t>90235</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8951,32 +8951,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>80549</t>
+          <t>82426</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>67781</t>
+          <t>69524</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>94155</t>
+          <t>96029</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8986,32 +8986,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>157487</t>
+          <t>158101</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>140175</t>
+          <t>139463</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>176488</t>
+          <t>177121</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -9029,17 +9029,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>295204</t>
+          <t>295306</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>295204</t>
+          <t>295306</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>295204</t>
+          <t>295306</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9064,17 +9064,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>339688</t>
+          <t>345942</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>339688</t>
+          <t>345942</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>339688</t>
+          <t>345942</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9099,17 +9099,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>634893</t>
+          <t>641248</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>634893</t>
+          <t>641248</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>634893</t>
+          <t>641248</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9146,32 +9146,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>28127</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>17741</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>34723</t>
+          <t>42393</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9181,32 +9181,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>31022</t>
+          <t>34299</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20884</t>
+          <t>25252</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43251</t>
+          <t>48625</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9216,32 +9216,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>53440</t>
+          <t>62426</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39041</t>
+          <t>48189</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>70625</t>
+          <t>82160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -9259,32 +9259,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>58278</t>
+          <t>67282</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44034</t>
+          <t>50922</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77603</t>
+          <t>84563</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9294,32 +9294,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>68455</t>
+          <t>75475</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>49863</t>
+          <t>62925</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>83988</t>
+          <t>91074</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9329,32 +9329,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>126732</t>
+          <t>142757</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>102035</t>
+          <t>121520</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>148804</t>
+          <t>164761</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,43%</t>
         </is>
       </c>
     </row>
@@ -9372,32 +9372,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>59443</t>
+          <t>71600</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43951</t>
+          <t>54342</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>75856</t>
+          <t>92878</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>108856</t>
+          <t>89527</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>79278</t>
+          <t>75789</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>174562</t>
+          <t>105375</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9442,32 +9442,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>168299</t>
+          <t>161127</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>136232</t>
+          <t>140094</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>242272</t>
+          <t>187184</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>20,77%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>27,76%</t>
         </is>
       </c>
     </row>
@@ -9485,32 +9485,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>51361</t>
+          <t>57734</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37262</t>
+          <t>41157</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>68977</t>
+          <t>77451</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9520,32 +9520,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>44506</t>
+          <t>51066</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>32345</t>
+          <t>40319</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>57437</t>
+          <t>63687</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9555,32 +9555,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>95866</t>
+          <t>108800</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>76611</t>
+          <t>88351</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>116715</t>
+          <t>132350</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -9598,32 +9598,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>67277</t>
+          <t>76990</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>53183</t>
+          <t>59207</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>83680</t>
+          <t>93950</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9633,32 +9633,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>109887</t>
+          <t>122271</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>80265</t>
+          <t>105702</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>129170</t>
+          <t>140500</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9668,32 +9668,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>177163</t>
+          <t>199261</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>145462</t>
+          <t>173284</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>202256</t>
+          <t>225283</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>28,51%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -9711,17 +9711,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>258776</t>
+          <t>301733</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>258776</t>
+          <t>301733</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>258776</t>
+          <t>301733</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9746,17 +9746,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>362726</t>
+          <t>372639</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>362726</t>
+          <t>372639</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>362726</t>
+          <t>372639</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9781,17 +9781,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>621501</t>
+          <t>674371</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>621501</t>
+          <t>674371</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>621501</t>
+          <t>674371</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9828,32 +9828,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>7207</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>12896</t>
+          <t>15059</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -9863,32 +9863,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8986</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>4689</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>13087</t>
+          <t>14214</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -9898,32 +9898,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>15343</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>10116</t>
+          <t>12326</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>22427</t>
+          <t>25597</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -9941,32 +9941,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>27218</t>
+          <t>30611</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>22552</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35973</t>
+          <t>39219</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -9976,32 +9976,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>31818</t>
+          <t>33347</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>25115</t>
+          <t>26510</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>39069</t>
+          <t>40214</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10011,32 +10011,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>59036</t>
+          <t>63958</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>49057</t>
+          <t>52877</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>70059</t>
+          <t>75590</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -10054,32 +10054,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>72263</t>
+          <t>78752</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>61879</t>
+          <t>68750</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>81872</t>
+          <t>89345</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>43,07%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>55,97%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10089,32 +10089,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>74975</t>
+          <t>80564</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>66636</t>
+          <t>72059</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>84371</t>
+          <t>90403</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10124,32 +10124,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>147237</t>
+          <t>159316</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>133899</t>
+          <t>145213</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>160294</t>
+          <t>173189</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -10167,32 +10167,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>24421</t>
+          <t>26391</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>18084</t>
+          <t>19330</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>33141</t>
+          <t>34607</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -10202,32 +10202,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>39473</t>
+          <t>41958</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33296</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>48213</t>
+          <t>51149</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>21,54%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -10237,32 +10237,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>63894</t>
+          <t>68349</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>54642</t>
+          <t>58133</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>75315</t>
+          <t>80154</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,55%</t>
         </is>
       </c>
     </row>
@@ -10280,32 +10280,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>14958</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9082</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>20296</t>
+          <t>21368</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -10315,32 +10315,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>28874</t>
+          <t>31019</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>23360</t>
+          <t>24362</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>35337</t>
+          <t>37978</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -10350,32 +10350,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>42811</t>
+          <t>45977</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>34809</t>
+          <t>37150</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>51263</t>
+          <t>55575</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -10393,17 +10393,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>145047</t>
+          <t>159625</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>145047</t>
+          <t>159625</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>145047</t>
+          <t>159625</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -10428,17 +10428,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>183275</t>
+          <t>195874</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>183275</t>
+          <t>195874</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>183275</t>
+          <t>195874</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -10463,17 +10463,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>328322</t>
+          <t>355499</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>328322</t>
+          <t>355499</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>328322</t>
+          <t>355499</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -10510,32 +10510,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>34768</t>
+          <t>34452</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>24819</t>
+          <t>24714</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>48111</t>
+          <t>46666</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -10545,32 +10545,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>23244</t>
+          <t>23384</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>15715</t>
+          <t>16130</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>31853</t>
+          <t>34120</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -10580,32 +10580,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>58012</t>
+          <t>57836</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>44715</t>
+          <t>46826</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>73446</t>
+          <t>74960</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -10623,32 +10623,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>61624</t>
+          <t>60600</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>49921</t>
+          <t>48273</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>75288</t>
+          <t>74098</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -10658,32 +10658,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>49000</t>
+          <t>50309</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>38208</t>
+          <t>39844</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>59362</t>
+          <t>61342</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -10693,32 +10693,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>110624</t>
+          <t>110909</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>93989</t>
+          <t>95275</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>128686</t>
+          <t>128836</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,42%</t>
         </is>
       </c>
     </row>
@@ -10736,32 +10736,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>66105</t>
+          <t>64906</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>54871</t>
+          <t>53463</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>78900</t>
+          <t>78267</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -10771,32 +10771,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>68832</t>
+          <t>70527</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>58254</t>
+          <t>59326</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>80198</t>
+          <t>83172</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -10806,32 +10806,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>134936</t>
+          <t>135433</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>119071</t>
+          <t>119151</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>153650</t>
+          <t>153469</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,28%</t>
         </is>
       </c>
     </row>
@@ -10849,32 +10849,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>39970</t>
+          <t>39541</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>30630</t>
+          <t>30663</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>50702</t>
+          <t>50180</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -10884,32 +10884,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>43403</t>
+          <t>44190</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>35411</t>
+          <t>35711</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>52726</t>
+          <t>53401</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>17,5%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -10919,32 +10919,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>83374</t>
+          <t>83731</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>70806</t>
+          <t>71332</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>96730</t>
+          <t>96615</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -10962,32 +10962,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>54682</t>
+          <t>53484</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>43652</t>
+          <t>43191</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>65610</t>
+          <t>65131</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -10997,32 +10997,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>63503</t>
+          <t>65495</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>54222</t>
+          <t>56129</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>74265</t>
+          <t>76638</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -11032,32 +11032,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>118185</t>
+          <t>118979</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>104581</t>
+          <t>103380</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>134701</t>
+          <t>132780</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -11075,17 +11075,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>257149</t>
+          <t>252982</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>257149</t>
+          <t>252982</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>257149</t>
+          <t>252982</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -11110,17 +11110,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>247982</t>
+          <t>253905</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>247982</t>
+          <t>253905</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>247982</t>
+          <t>253905</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -11145,17 +11145,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>505131</t>
+          <t>506887</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>505131</t>
+          <t>506887</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>505131</t>
+          <t>506887</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -11192,32 +11192,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>28053</t>
+          <t>39087</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>19139</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>39580</t>
+          <t>53513</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -11227,32 +11227,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>30693</t>
+          <t>34726</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>25064</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>47023</t>
+          <t>47172</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -11262,32 +11262,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>58746</t>
+          <t>73814</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>33237</t>
+          <t>57929</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>78878</t>
+          <t>91617</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -11305,32 +11305,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>91587</t>
+          <t>105793</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>73783</t>
+          <t>84384</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>115052</t>
+          <t>129047</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -11340,32 +11340,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>107903</t>
+          <t>129045</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>52461</t>
+          <t>110676</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>155135</t>
+          <t>151235</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -11375,32 +11375,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>199489</t>
+          <t>234838</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>118963</t>
+          <t>203753</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>248470</t>
+          <t>265848</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -11418,32 +11418,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>169689</t>
+          <t>195144</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>145491</t>
+          <t>170898</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>194485</t>
+          <t>221220</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>384136</t>
+          <t>209711</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>232617</t>
+          <t>187646</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>594457</t>
+          <t>233307</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -11488,32 +11488,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>553826</t>
+          <t>404855</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>403161</t>
+          <t>368132</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>817276</t>
+          <t>440496</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>31,91%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>34,72%</t>
         </is>
       </c>
     </row>
@@ -11531,27 +11531,27 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>88154</t>
+          <t>104840</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>72605</t>
+          <t>87628</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>107535</t>
+          <t>126118</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>96861</t>
+          <t>116910</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>42355</t>
+          <t>100460</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>138153</t>
+          <t>135469</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -11601,32 +11601,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>185015</t>
+          <t>221750</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>114862</t>
+          <t>196778</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>228899</t>
+          <t>249060</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -11644,32 +11644,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>116977</t>
+          <t>134863</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>97427</t>
+          <t>115214</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>134670</t>
+          <t>158556</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -11679,32 +11679,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>162425</t>
+          <t>198609</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>72254</t>
+          <t>178031</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>229064</t>
+          <t>221973</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -11714,32 +11714,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>279402</t>
+          <t>333472</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>179320</t>
+          <t>302218</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>345095</t>
+          <t>366894</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>28,92%</t>
         </is>
       </c>
     </row>
@@ -11757,17 +11757,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>494459</t>
+          <t>579727</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>494459</t>
+          <t>579727</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>494459</t>
+          <t>579727</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -11792,17 +11792,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>782019</t>
+          <t>689001</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>782019</t>
+          <t>689001</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>782019</t>
+          <t>689001</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -11827,17 +11827,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>1276478</t>
+          <t>1268728</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>1276478</t>
+          <t>1268728</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>1276478</t>
+          <t>1268728</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>19957</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>12297</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>24297</t>
+          <t>30162</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -11909,67 +11909,67 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>20694</t>
+          <t>23451</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>16280</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>29389</t>
+          <t>32960</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>5,75%</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>43408</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>32312</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>56904</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
           <t>4,14%</t>
         </is>
       </c>
-      <c r="O46" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="P46" s="2" t="inlineStr">
-        <is>
-          <t>5,89%</t>
-        </is>
-      </c>
-      <c r="Q46" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="R46" s="2" t="inlineStr">
-        <is>
-          <t>35996</t>
-        </is>
-      </c>
-      <c r="S46" s="2" t="inlineStr">
-        <is>
-          <t>27007</t>
-        </is>
-      </c>
-      <c r="T46" s="2" t="inlineStr">
-        <is>
-          <t>48109</t>
-        </is>
-      </c>
-      <c r="U46" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -11987,32 +11987,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>134886</t>
+          <t>153113</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>117937</t>
+          <t>133729</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>153938</t>
+          <t>172019</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -12022,32 +12022,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>132248</t>
+          <t>151613</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>115857</t>
+          <t>132832</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>149533</t>
+          <t>168421</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -12057,32 +12057,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>267134</t>
+          <t>304726</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>242973</t>
+          <t>278955</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>290512</t>
+          <t>330928</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,59%</t>
         </is>
       </c>
     </row>
@@ -12100,32 +12100,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>141520</t>
+          <t>159018</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>125619</t>
+          <t>141604</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>158721</t>
+          <t>179967</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -12135,32 +12135,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>174702</t>
+          <t>202032</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>158845</t>
+          <t>183140</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>192553</t>
+          <t>221247</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -12170,17 +12170,17 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>316222</t>
+          <t>361050</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>292412</t>
+          <t>333629</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>341824</t>
+          <t>389220</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -12190,12 +12190,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,16%</t>
         </is>
       </c>
     </row>
@@ -12213,32 +12213,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>101712</t>
+          <t>114288</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>86334</t>
+          <t>98242</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>117939</t>
+          <t>130456</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -12248,32 +12248,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>113052</t>
+          <t>129112</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>100473</t>
+          <t>113500</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>129333</t>
+          <t>147683</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -12283,32 +12283,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>214764</t>
+          <t>243400</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>193349</t>
+          <t>222150</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>236355</t>
+          <t>269161</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>23,41%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -12326,17 +12326,17 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>24710</t>
+          <t>28050</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>16712</t>
+          <t>18803</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>34658</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -12346,12 +12346,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -12361,32 +12361,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>58609</t>
+          <t>66877</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>48107</t>
+          <t>54781</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>70168</t>
+          <t>81049</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -12396,32 +12396,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>83319</t>
+          <t>94927</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>69207</t>
+          <t>79851</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>98558</t>
+          <t>112140</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -12439,17 +12439,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>418130</t>
+          <t>474426</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>418130</t>
+          <t>474426</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>418130</t>
+          <t>474426</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -12474,17 +12474,17 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>499305</t>
+          <t>573085</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>499305</t>
+          <t>573085</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>499305</t>
+          <t>573085</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -12509,17 +12509,17 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>917435</t>
+          <t>1047511</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>917435</t>
+          <t>1047511</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>917435</t>
+          <t>1047511</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -12556,32 +12556,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>219452</t>
+          <t>248042</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>189985</t>
+          <t>213635</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>253249</t>
+          <t>282025</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -12591,32 +12591,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>214681</t>
+          <t>231439</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>169140</t>
+          <t>206786</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>245341</t>
+          <t>258619</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -12626,32 +12626,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>434133</t>
+          <t>479481</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>376305</t>
+          <t>439419</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>477555</t>
+          <t>525776</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -12669,32 +12669,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>668869</t>
+          <t>731310</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>624114</t>
+          <t>688161</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>719194</t>
+          <t>781603</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -12704,32 +12704,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>699768</t>
+          <t>775679</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>514877</t>
+          <t>734943</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>764924</t>
+          <t>822304</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -12739,32 +12739,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>1368637</t>
+          <t>1506990</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>1198206</t>
+          <t>1439289</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>1452035</t>
+          <t>1574921</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -12782,32 +12782,32 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>754872</t>
+          <t>808088</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>709204</t>
+          <t>758096</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>807642</t>
+          <t>858923</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
@@ -12817,32 +12817,32 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>1084229</t>
+          <t>934644</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>917760</t>
+          <t>890895</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>1561249</t>
+          <t>977844</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -12852,32 +12852,32 @@
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>1839101</t>
+          <t>1742732</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>1666576</t>
+          <t>1678391</t>
         </is>
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>2360790</t>
+          <t>1814012</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>30,38%</t>
         </is>
       </c>
     </row>
@@ -12895,22 +12895,22 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>425664</t>
+          <t>462637</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>388860</t>
+          <t>422086</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>465000</t>
+          <t>507319</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -12920,7 +12920,7 @@
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
@@ -12930,32 +12930,32 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>471211</t>
+          <t>524211</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>371900</t>
+          <t>491429</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>521615</t>
+          <t>561460</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -12965,32 +12965,32 @@
       </c>
       <c r="R55" s="2" t="inlineStr">
         <is>
-          <t>896876</t>
+          <t>986847</t>
         </is>
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>794632</t>
+          <t>937906</t>
         </is>
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>966083</t>
+          <t>1043420</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -13008,32 +13008,32 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>483425</t>
+          <t>519857</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>443283</t>
+          <t>477579</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>522492</t>
+          <t>562589</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
@@ -13043,32 +13043,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>663053</t>
+          <t>734196</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>527623</t>
+          <t>691994</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>726740</t>
+          <t>772919</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -13078,32 +13078,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>1146478</t>
+          <t>1254053</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>1002787</t>
+          <t>1199179</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>1217733</t>
+          <t>1316351</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>22,05%</t>
         </is>
       </c>
     </row>
@@ -13121,17 +13121,17 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>2552282</t>
+          <t>2769934</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>2552282</t>
+          <t>2769934</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>2552282</t>
+          <t>2769934</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
@@ -13156,17 +13156,17 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>3132942</t>
+          <t>3200169</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>3132942</t>
+          <t>3200169</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3132942</t>
+          <t>3200169</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -13191,17 +13191,17 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>5685225</t>
+          <t>5970103</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>5685225</t>
+          <t>5970103</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>5685225</t>
+          <t>5970103</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
